--- a/data/vannmiljo_duplicates_stations.xlsx
+++ b/data/vannmiljo_duplicates_stations.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC669"/>
+  <dimension ref="A1:AC677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77821,12 +77821,12 @@
       </c>
       <c r="V582" t="inlineStr">
         <is>
-          <t>Vannområde Øyeren</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W582" t="inlineStr">
         <is>
-          <t>Felt: Norconsult AS, Lab: NorAnalyse</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X582" t="inlineStr">
@@ -77835,7 +77835,7 @@
         </is>
       </c>
       <c r="Y582" s="2" t="n">
-        <v>42960</v>
+        <v>46125</v>
       </c>
       <c r="Z582" t="n">
         <v>0</v>
@@ -77844,11 +77844,11 @@
         <v>0</v>
       </c>
       <c r="AB582" t="n">
-        <v>11</v>
+        <v>490</v>
       </c>
       <c r="AC582" t="inlineStr">
         <is>
-          <t>TOC_Ufilt_mg/l C</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -77954,12 +77954,12 @@
       </c>
       <c r="V583" t="inlineStr">
         <is>
-          <t>Vannområde Øyeren</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W583" t="inlineStr">
         <is>
-          <t>Felt: Norconsult AS, Lab: NorAnalyse</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X583" t="inlineStr">
@@ -77968,7 +77968,7 @@
         </is>
       </c>
       <c r="Y583" s="2" t="n">
-        <v>42960</v>
+        <v>46125</v>
       </c>
       <c r="Z583" t="n">
         <v>0</v>
@@ -77977,26 +77977,26 @@
         <v>0</v>
       </c>
       <c r="AB583" t="n">
-        <v>18</v>
+        <v>580</v>
       </c>
       <c r="AC583" t="inlineStr">
         <is>
-          <t>TOC_Ufilt_mg/l C</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -78005,10 +78005,10 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F584" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G584" t="inlineStr">
         <is>
@@ -78042,12 +78042,12 @@
       </c>
       <c r="M584" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O584" t="inlineStr">
@@ -78062,12 +78062,12 @@
       </c>
       <c r="Q584" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R584" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S584" t="inlineStr">
@@ -78087,12 +78087,12 @@
       </c>
       <c r="V584" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W584" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X584" t="inlineStr">
@@ -78101,7 +78101,7 @@
         </is>
       </c>
       <c r="Y584" s="2" t="n">
-        <v>39932</v>
+        <v>46153</v>
       </c>
       <c r="Z584" t="n">
         <v>0</v>
@@ -78110,26 +78110,26 @@
         <v>0</v>
       </c>
       <c r="AB584" t="n">
-        <v>650</v>
+        <v>380</v>
       </c>
       <c r="AC584" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -78138,10 +78138,10 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F585" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G585" t="inlineStr">
         <is>
@@ -78175,12 +78175,12 @@
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O585" t="inlineStr">
@@ -78195,12 +78195,12 @@
       </c>
       <c r="Q585" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R585" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S585" t="inlineStr">
@@ -78220,12 +78220,12 @@
       </c>
       <c r="V585" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W585" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X585" t="inlineStr">
@@ -78234,7 +78234,7 @@
         </is>
       </c>
       <c r="Y585" s="2" t="n">
-        <v>39932</v>
+        <v>46153</v>
       </c>
       <c r="Z585" t="n">
         <v>0</v>
@@ -78243,26 +78243,26 @@
         <v>0</v>
       </c>
       <c r="AB585" t="n">
-        <v>650</v>
+        <v>380</v>
       </c>
       <c r="AC585" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -78271,10 +78271,10 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F586" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G586" t="inlineStr">
         <is>
@@ -78308,12 +78308,12 @@
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
@@ -78328,12 +78328,12 @@
       </c>
       <c r="Q586" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R586" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S586" t="inlineStr">
@@ -78353,12 +78353,12 @@
       </c>
       <c r="V586" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W586" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X586" t="inlineStr">
@@ -78367,7 +78367,7 @@
         </is>
       </c>
       <c r="Y586" s="2" t="n">
-        <v>39932</v>
+        <v>46170</v>
       </c>
       <c r="Z586" t="n">
         <v>0</v>
@@ -78376,26 +78376,26 @@
         <v>0</v>
       </c>
       <c r="AB586" t="n">
-        <v>650</v>
+        <v>510</v>
       </c>
       <c r="AC586" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -78404,10 +78404,10 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F587" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G587" t="inlineStr">
         <is>
@@ -78441,12 +78441,12 @@
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O587" t="inlineStr">
@@ -78461,12 +78461,12 @@
       </c>
       <c r="Q587" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R587" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S587" t="inlineStr">
@@ -78486,12 +78486,12 @@
       </c>
       <c r="V587" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W587" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X587" t="inlineStr">
@@ -78500,7 +78500,7 @@
         </is>
       </c>
       <c r="Y587" s="2" t="n">
-        <v>39932</v>
+        <v>46170</v>
       </c>
       <c r="Z587" t="n">
         <v>0</v>
@@ -78509,26 +78509,26 @@
         <v>0</v>
       </c>
       <c r="AB587" t="n">
-        <v>650</v>
+        <v>470</v>
       </c>
       <c r="AC587" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -78537,10 +78537,10 @@
         </is>
       </c>
       <c r="E588" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F588" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G588" t="inlineStr">
         <is>
@@ -78574,12 +78574,12 @@
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O588" t="inlineStr">
@@ -78594,12 +78594,12 @@
       </c>
       <c r="Q588" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R588" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S588" t="inlineStr">
@@ -78619,12 +78619,12 @@
       </c>
       <c r="V588" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W588" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X588" t="inlineStr">
@@ -78633,7 +78633,7 @@
         </is>
       </c>
       <c r="Y588" s="2" t="n">
-        <v>39932</v>
+        <v>46182</v>
       </c>
       <c r="Z588" t="n">
         <v>0</v>
@@ -78642,26 +78642,26 @@
         <v>0</v>
       </c>
       <c r="AB588" t="n">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="AC588" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -78670,10 +78670,10 @@
         </is>
       </c>
       <c r="E589" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F589" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G589" t="inlineStr">
         <is>
@@ -78707,12 +78707,12 @@
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O589" t="inlineStr">
@@ -78727,12 +78727,12 @@
       </c>
       <c r="Q589" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R589" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S589" t="inlineStr">
@@ -78752,12 +78752,12 @@
       </c>
       <c r="V589" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Nes kommune</t>
         </is>
       </c>
       <c r="W589" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Eurofins Environment Testing Norway (Moss)</t>
         </is>
       </c>
       <c r="X589" t="inlineStr">
@@ -78766,7 +78766,7 @@
         </is>
       </c>
       <c r="Y589" s="2" t="n">
-        <v>39932</v>
+        <v>46182</v>
       </c>
       <c r="Z589" t="n">
         <v>0</v>
@@ -78775,26 +78775,26 @@
         <v>0</v>
       </c>
       <c r="AB589" t="n">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="AC589" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-NO3_Filt_µg/l N</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -78803,10 +78803,10 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F590" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G590" t="inlineStr">
         <is>
@@ -78840,12 +78840,12 @@
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O590" t="inlineStr">
@@ -78860,12 +78860,12 @@
       </c>
       <c r="Q590" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R590" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S590" t="inlineStr">
@@ -78885,12 +78885,12 @@
       </c>
       <c r="V590" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Vannområde Øyeren</t>
         </is>
       </c>
       <c r="W590" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Felt: Norconsult AS, Lab: NorAnalyse</t>
         </is>
       </c>
       <c r="X590" t="inlineStr">
@@ -78899,7 +78899,7 @@
         </is>
       </c>
       <c r="Y590" s="2" t="n">
-        <v>39932</v>
+        <v>42960</v>
       </c>
       <c r="Z590" t="n">
         <v>0</v>
@@ -78908,26 +78908,26 @@
         <v>0</v>
       </c>
       <c r="AB590" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AC590" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>TOC_Ufilt_mg/l C</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>63540</v>
+        <v>60933</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>002-63540</t>
+          <t>002-60933</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Fjellhammarelva (F10)</t>
+          <t>Gansåa nedstrøms Dalen RA</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -78936,10 +78936,10 @@
         </is>
       </c>
       <c r="E591" t="n">
-        <v>276390.4391999999</v>
+        <v>288509.2999999998</v>
       </c>
       <c r="F591" t="n">
-        <v>6651962.844799999</v>
+        <v>6642006.800000001</v>
       </c>
       <c r="G591" t="inlineStr">
         <is>
@@ -78973,12 +78973,12 @@
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
@@ -78993,12 +78993,12 @@
       </c>
       <c r="Q591" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3655-R</t>
         </is>
       </c>
       <c r="R591" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Gansåa</t>
         </is>
       </c>
       <c r="S591" t="inlineStr">
@@ -79018,12 +79018,12 @@
       </c>
       <c r="V591" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Vannområde Øyeren</t>
         </is>
       </c>
       <c r="W591" t="inlineStr">
         <is>
-          <t>Lørenskog kommune</t>
+          <t>Felt: Norconsult AS, Lab: NorAnalyse</t>
         </is>
       </c>
       <c r="X591" t="inlineStr">
@@ -79032,7 +79032,7 @@
         </is>
       </c>
       <c r="Y591" s="2" t="n">
-        <v>39932</v>
+        <v>42960</v>
       </c>
       <c r="Z591" t="n">
         <v>0</v>
@@ -79041,11 +79041,11 @@
         <v>0</v>
       </c>
       <c r="AB591" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AC591" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>TOC_Ufilt_mg/l C</t>
         </is>
       </c>
     </row>
@@ -79165,7 +79165,7 @@
         </is>
       </c>
       <c r="Y592" s="2" t="n">
-        <v>39939</v>
+        <v>39932</v>
       </c>
       <c r="Z592" t="n">
         <v>0</v>
@@ -79174,11 +79174,11 @@
         <v>0</v>
       </c>
       <c r="AB592" t="n">
-        <v>16</v>
+        <v>650</v>
       </c>
       <c r="AC592" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -79298,7 +79298,7 @@
         </is>
       </c>
       <c r="Y593" s="2" t="n">
-        <v>39939</v>
+        <v>39932</v>
       </c>
       <c r="Z593" t="n">
         <v>0</v>
@@ -79307,11 +79307,11 @@
         <v>0</v>
       </c>
       <c r="AB593" t="n">
-        <v>16</v>
+        <v>650</v>
       </c>
       <c r="AC593" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -79431,7 +79431,7 @@
         </is>
       </c>
       <c r="Y594" s="2" t="n">
-        <v>39946</v>
+        <v>39932</v>
       </c>
       <c r="Z594" t="n">
         <v>0</v>
@@ -79440,7 +79440,7 @@
         <v>0</v>
       </c>
       <c r="AB594" t="n">
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="AC594" t="inlineStr">
         <is>
@@ -79564,7 +79564,7 @@
         </is>
       </c>
       <c r="Y595" s="2" t="n">
-        <v>39946</v>
+        <v>39932</v>
       </c>
       <c r="Z595" t="n">
         <v>0</v>
@@ -79573,7 +79573,7 @@
         <v>0</v>
       </c>
       <c r="AB595" t="n">
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="AC595" t="inlineStr">
         <is>
@@ -79697,7 +79697,7 @@
         </is>
       </c>
       <c r="Y596" s="2" t="n">
-        <v>39946</v>
+        <v>39932</v>
       </c>
       <c r="Z596" t="n">
         <v>0</v>
@@ -79706,7 +79706,7 @@
         <v>0</v>
       </c>
       <c r="AB596" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC596" t="inlineStr">
         <is>
@@ -79830,7 +79830,7 @@
         </is>
       </c>
       <c r="Y597" s="2" t="n">
-        <v>39946</v>
+        <v>39932</v>
       </c>
       <c r="Z597" t="n">
         <v>0</v>
@@ -79839,7 +79839,7 @@
         <v>0</v>
       </c>
       <c r="AB597" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC597" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         </is>
       </c>
       <c r="Y598" s="2" t="n">
-        <v>39946</v>
+        <v>39932</v>
       </c>
       <c r="Z598" t="n">
         <v>0</v>
@@ -79972,7 +79972,7 @@
         <v>0</v>
       </c>
       <c r="AB598" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AC598" t="inlineStr">
         <is>
@@ -80096,7 +80096,7 @@
         </is>
       </c>
       <c r="Y599" s="2" t="n">
-        <v>39946</v>
+        <v>39932</v>
       </c>
       <c r="Z599" t="n">
         <v>0</v>
@@ -80105,7 +80105,7 @@
         <v>0</v>
       </c>
       <c r="AB599" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AC599" t="inlineStr">
         <is>
@@ -80229,7 +80229,7 @@
         </is>
       </c>
       <c r="Y600" s="2" t="n">
-        <v>39952</v>
+        <v>39939</v>
       </c>
       <c r="Z600" t="n">
         <v>0</v>
@@ -80238,11 +80238,11 @@
         <v>0</v>
       </c>
       <c r="AB600" t="n">
-        <v>620</v>
+        <v>16</v>
       </c>
       <c r="AC600" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -80362,7 +80362,7 @@
         </is>
       </c>
       <c r="Y601" s="2" t="n">
-        <v>39952</v>
+        <v>39939</v>
       </c>
       <c r="Z601" t="n">
         <v>0</v>
@@ -80371,11 +80371,11 @@
         <v>0</v>
       </c>
       <c r="AB601" t="n">
-        <v>620</v>
+        <v>16</v>
       </c>
       <c r="AC601" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -80495,7 +80495,7 @@
         </is>
       </c>
       <c r="Y602" s="2" t="n">
-        <v>39952</v>
+        <v>39946</v>
       </c>
       <c r="Z602" t="n">
         <v>0</v>
@@ -80504,11 +80504,11 @@
         <v>0</v>
       </c>
       <c r="AB602" t="n">
-        <v>2</v>
+        <v>710</v>
       </c>
       <c r="AC602" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -80628,7 +80628,7 @@
         </is>
       </c>
       <c r="Y603" s="2" t="n">
-        <v>39952</v>
+        <v>39946</v>
       </c>
       <c r="Z603" t="n">
         <v>0</v>
@@ -80637,11 +80637,11 @@
         <v>0</v>
       </c>
       <c r="AB603" t="n">
-        <v>2</v>
+        <v>710</v>
       </c>
       <c r="AC603" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -80761,7 +80761,7 @@
         </is>
       </c>
       <c r="Y604" s="2" t="n">
-        <v>39952</v>
+        <v>39946</v>
       </c>
       <c r="Z604" t="n">
         <v>0</v>
@@ -80770,11 +80770,11 @@
         <v>0</v>
       </c>
       <c r="AB604" t="n">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="AC604" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -80894,7 +80894,7 @@
         </is>
       </c>
       <c r="Y605" s="2" t="n">
-        <v>39952</v>
+        <v>39946</v>
       </c>
       <c r="Z605" t="n">
         <v>0</v>
@@ -80903,11 +80903,11 @@
         <v>0</v>
       </c>
       <c r="AB605" t="n">
-        <v>3.9</v>
+        <v>23</v>
       </c>
       <c r="AC605" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -81027,7 +81027,7 @@
         </is>
       </c>
       <c r="Y606" s="2" t="n">
-        <v>39959</v>
+        <v>39946</v>
       </c>
       <c r="Z606" t="n">
         <v>0</v>
@@ -81036,11 +81036,11 @@
         <v>0</v>
       </c>
       <c r="AB606" t="n">
-        <v>720</v>
+        <v>4</v>
       </c>
       <c r="AC606" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -81160,7 +81160,7 @@
         </is>
       </c>
       <c r="Y607" s="2" t="n">
-        <v>39959</v>
+        <v>39946</v>
       </c>
       <c r="Z607" t="n">
         <v>0</v>
@@ -81169,11 +81169,11 @@
         <v>0</v>
       </c>
       <c r="AB607" t="n">
-        <v>720</v>
+        <v>4</v>
       </c>
       <c r="AC607" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -81293,7 +81293,7 @@
         </is>
       </c>
       <c r="Y608" s="2" t="n">
-        <v>39959</v>
+        <v>39952</v>
       </c>
       <c r="Z608" t="n">
         <v>0</v>
@@ -81302,11 +81302,11 @@
         <v>0</v>
       </c>
       <c r="AB608" t="n">
-        <v>22</v>
+        <v>620</v>
       </c>
       <c r="AC608" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -81426,7 +81426,7 @@
         </is>
       </c>
       <c r="Y609" s="2" t="n">
-        <v>39959</v>
+        <v>39952</v>
       </c>
       <c r="Z609" t="n">
         <v>0</v>
@@ -81435,11 +81435,11 @@
         <v>0</v>
       </c>
       <c r="AB609" t="n">
-        <v>22</v>
+        <v>620</v>
       </c>
       <c r="AC609" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -81559,7 +81559,7 @@
         </is>
       </c>
       <c r="Y610" s="2" t="n">
-        <v>39959</v>
+        <v>39952</v>
       </c>
       <c r="Z610" t="n">
         <v>0</v>
@@ -81568,11 +81568,11 @@
         <v>0</v>
       </c>
       <c r="AB610" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC610" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -81692,7 +81692,7 @@
         </is>
       </c>
       <c r="Y611" s="2" t="n">
-        <v>39959</v>
+        <v>39952</v>
       </c>
       <c r="Z611" t="n">
         <v>0</v>
@@ -81701,11 +81701,11 @@
         <v>0</v>
       </c>
       <c r="AB611" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC611" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -81825,7 +81825,7 @@
         </is>
       </c>
       <c r="Y612" s="2" t="n">
-        <v>39974</v>
+        <v>39952</v>
       </c>
       <c r="Z612" t="n">
         <v>0</v>
@@ -81834,11 +81834,11 @@
         <v>0</v>
       </c>
       <c r="AB612" t="n">
-        <v>570</v>
+        <v>3.9</v>
       </c>
       <c r="AC612" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -81958,7 +81958,7 @@
         </is>
       </c>
       <c r="Y613" s="2" t="n">
-        <v>39974</v>
+        <v>39952</v>
       </c>
       <c r="Z613" t="n">
         <v>0</v>
@@ -81967,11 +81967,11 @@
         <v>0</v>
       </c>
       <c r="AB613" t="n">
-        <v>570</v>
+        <v>3.9</v>
       </c>
       <c r="AC613" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -82091,7 +82091,7 @@
         </is>
       </c>
       <c r="Y614" s="2" t="n">
-        <v>39974</v>
+        <v>39959</v>
       </c>
       <c r="Z614" t="n">
         <v>0</v>
@@ -82100,11 +82100,11 @@
         <v>0</v>
       </c>
       <c r="AB614" t="n">
-        <v>5.1</v>
+        <v>720</v>
       </c>
       <c r="AC614" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -82224,7 +82224,7 @@
         </is>
       </c>
       <c r="Y615" s="2" t="n">
-        <v>39974</v>
+        <v>39959</v>
       </c>
       <c r="Z615" t="n">
         <v>0</v>
@@ -82233,11 +82233,11 @@
         <v>0</v>
       </c>
       <c r="AB615" t="n">
-        <v>5.1</v>
+        <v>720</v>
       </c>
       <c r="AC615" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -82357,7 +82357,7 @@
         </is>
       </c>
       <c r="Y616" s="2" t="n">
-        <v>39988</v>
+        <v>39959</v>
       </c>
       <c r="Z616" t="n">
         <v>0</v>
@@ -82366,11 +82366,11 @@
         <v>0</v>
       </c>
       <c r="AB616" t="n">
-        <v>740</v>
+        <v>22</v>
       </c>
       <c r="AC616" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -82490,7 +82490,7 @@
         </is>
       </c>
       <c r="Y617" s="2" t="n">
-        <v>39988</v>
+        <v>39959</v>
       </c>
       <c r="Z617" t="n">
         <v>0</v>
@@ -82499,11 +82499,11 @@
         <v>0</v>
       </c>
       <c r="AB617" t="n">
-        <v>740</v>
+        <v>22</v>
       </c>
       <c r="AC617" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -82623,7 +82623,7 @@
         </is>
       </c>
       <c r="Y618" s="2" t="n">
-        <v>39988</v>
+        <v>39959</v>
       </c>
       <c r="Z618" t="n">
         <v>0</v>
@@ -82632,11 +82632,11 @@
         <v>0</v>
       </c>
       <c r="AB618" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AC618" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -82756,7 +82756,7 @@
         </is>
       </c>
       <c r="Y619" s="2" t="n">
-        <v>39988</v>
+        <v>39959</v>
       </c>
       <c r="Z619" t="n">
         <v>0</v>
@@ -82765,11 +82765,11 @@
         <v>0</v>
       </c>
       <c r="AB619" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AC619" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -82889,7 +82889,7 @@
         </is>
       </c>
       <c r="Y620" s="2" t="n">
-        <v>39988</v>
+        <v>39974</v>
       </c>
       <c r="Z620" t="n">
         <v>0</v>
@@ -82898,11 +82898,11 @@
         <v>0</v>
       </c>
       <c r="AB620" t="n">
-        <v>5.4</v>
+        <v>570</v>
       </c>
       <c r="AC620" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -83022,7 +83022,7 @@
         </is>
       </c>
       <c r="Y621" s="2" t="n">
-        <v>39988</v>
+        <v>39974</v>
       </c>
       <c r="Z621" t="n">
         <v>0</v>
@@ -83031,11 +83031,11 @@
         <v>0</v>
       </c>
       <c r="AB621" t="n">
-        <v>5.4</v>
+        <v>570</v>
       </c>
       <c r="AC621" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -83155,7 +83155,7 @@
         </is>
       </c>
       <c r="Y622" s="2" t="n">
-        <v>39995</v>
+        <v>39974</v>
       </c>
       <c r="Z622" t="n">
         <v>0</v>
@@ -83164,11 +83164,11 @@
         <v>0</v>
       </c>
       <c r="AB622" t="n">
-        <v>700</v>
+        <v>5.1</v>
       </c>
       <c r="AC622" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -83288,7 +83288,7 @@
         </is>
       </c>
       <c r="Y623" s="2" t="n">
-        <v>39995</v>
+        <v>39974</v>
       </c>
       <c r="Z623" t="n">
         <v>0</v>
@@ -83297,11 +83297,11 @@
         <v>0</v>
       </c>
       <c r="AB623" t="n">
-        <v>700</v>
+        <v>5.1</v>
       </c>
       <c r="AC623" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -83421,7 +83421,7 @@
         </is>
       </c>
       <c r="Y624" s="2" t="n">
-        <v>39995</v>
+        <v>39988</v>
       </c>
       <c r="Z624" t="n">
         <v>0</v>
@@ -83430,11 +83430,11 @@
         <v>0</v>
       </c>
       <c r="AB624" t="n">
-        <v>12</v>
+        <v>740</v>
       </c>
       <c r="AC624" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -83554,7 +83554,7 @@
         </is>
       </c>
       <c r="Y625" s="2" t="n">
-        <v>39995</v>
+        <v>39988</v>
       </c>
       <c r="Z625" t="n">
         <v>0</v>
@@ -83563,11 +83563,11 @@
         <v>0</v>
       </c>
       <c r="AB625" t="n">
-        <v>12</v>
+        <v>740</v>
       </c>
       <c r="AC625" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -83687,7 +83687,7 @@
         </is>
       </c>
       <c r="Y626" s="2" t="n">
-        <v>39995</v>
+        <v>39988</v>
       </c>
       <c r="Z626" t="n">
         <v>0</v>
@@ -83696,11 +83696,11 @@
         <v>0</v>
       </c>
       <c r="AB626" t="n">
-        <v>6.3</v>
+        <v>24</v>
       </c>
       <c r="AC626" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -83820,7 +83820,7 @@
         </is>
       </c>
       <c r="Y627" s="2" t="n">
-        <v>39995</v>
+        <v>39988</v>
       </c>
       <c r="Z627" t="n">
         <v>0</v>
@@ -83829,11 +83829,11 @@
         <v>0</v>
       </c>
       <c r="AB627" t="n">
-        <v>6.3</v>
+        <v>24</v>
       </c>
       <c r="AC627" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -83953,7 +83953,7 @@
         </is>
       </c>
       <c r="Y628" s="2" t="n">
-        <v>40002</v>
+        <v>39988</v>
       </c>
       <c r="Z628" t="n">
         <v>0</v>
@@ -83962,11 +83962,11 @@
         <v>0</v>
       </c>
       <c r="AB628" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="AC628" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -84086,7 +84086,7 @@
         </is>
       </c>
       <c r="Y629" s="2" t="n">
-        <v>40002</v>
+        <v>39988</v>
       </c>
       <c r="Z629" t="n">
         <v>0</v>
@@ -84095,11 +84095,11 @@
         <v>0</v>
       </c>
       <c r="AB629" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="AC629" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -84219,7 +84219,7 @@
         </is>
       </c>
       <c r="Y630" s="2" t="n">
-        <v>40002</v>
+        <v>39995</v>
       </c>
       <c r="Z630" t="n">
         <v>0</v>
@@ -84228,11 +84228,11 @@
         <v>0</v>
       </c>
       <c r="AB630" t="n">
-        <v>53</v>
+        <v>700</v>
       </c>
       <c r="AC630" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -84352,7 +84352,7 @@
         </is>
       </c>
       <c r="Y631" s="2" t="n">
-        <v>40002</v>
+        <v>39995</v>
       </c>
       <c r="Z631" t="n">
         <v>0</v>
@@ -84361,11 +84361,11 @@
         <v>0</v>
       </c>
       <c r="AB631" t="n">
-        <v>53</v>
+        <v>700</v>
       </c>
       <c r="AC631" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -84485,7 +84485,7 @@
         </is>
       </c>
       <c r="Y632" s="2" t="n">
-        <v>40002</v>
+        <v>39995</v>
       </c>
       <c r="Z632" t="n">
         <v>0</v>
@@ -84494,11 +84494,11 @@
         <v>0</v>
       </c>
       <c r="AB632" t="n">
-        <v>6.3</v>
+        <v>12</v>
       </c>
       <c r="AC632" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -84618,7 +84618,7 @@
         </is>
       </c>
       <c r="Y633" s="2" t="n">
-        <v>40002</v>
+        <v>39995</v>
       </c>
       <c r="Z633" t="n">
         <v>0</v>
@@ -84627,11 +84627,11 @@
         <v>0</v>
       </c>
       <c r="AB633" t="n">
-        <v>6.3</v>
+        <v>12</v>
       </c>
       <c r="AC633" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -84751,7 +84751,7 @@
         </is>
       </c>
       <c r="Y634" s="2" t="n">
-        <v>40009</v>
+        <v>39995</v>
       </c>
       <c r="Z634" t="n">
         <v>0</v>
@@ -84760,11 +84760,11 @@
         <v>0</v>
       </c>
       <c r="AB634" t="n">
-        <v>600</v>
+        <v>6.3</v>
       </c>
       <c r="AC634" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -84884,7 +84884,7 @@
         </is>
       </c>
       <c r="Y635" s="2" t="n">
-        <v>40009</v>
+        <v>39995</v>
       </c>
       <c r="Z635" t="n">
         <v>0</v>
@@ -84893,11 +84893,11 @@
         <v>0</v>
       </c>
       <c r="AB635" t="n">
-        <v>600</v>
+        <v>6.3</v>
       </c>
       <c r="AC635" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -85017,7 +85017,7 @@
         </is>
       </c>
       <c r="Y636" s="2" t="n">
-        <v>40009</v>
+        <v>40002</v>
       </c>
       <c r="Z636" t="n">
         <v>0</v>
@@ -85026,11 +85026,11 @@
         <v>0</v>
       </c>
       <c r="AB636" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC636" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -85150,7 +85150,7 @@
         </is>
       </c>
       <c r="Y637" s="2" t="n">
-        <v>40009</v>
+        <v>40002</v>
       </c>
       <c r="Z637" t="n">
         <v>0</v>
@@ -85159,11 +85159,11 @@
         <v>0</v>
       </c>
       <c r="AB637" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC637" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -85283,7 +85283,7 @@
         </is>
       </c>
       <c r="Y638" s="2" t="n">
-        <v>40009</v>
+        <v>40002</v>
       </c>
       <c r="Z638" t="n">
         <v>0</v>
@@ -85292,11 +85292,11 @@
         <v>0</v>
       </c>
       <c r="AB638" t="n">
-        <v>7.2</v>
+        <v>53</v>
       </c>
       <c r="AC638" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -85416,7 +85416,7 @@
         </is>
       </c>
       <c r="Y639" s="2" t="n">
-        <v>40009</v>
+        <v>40002</v>
       </c>
       <c r="Z639" t="n">
         <v>0</v>
@@ -85425,11 +85425,11 @@
         <v>0</v>
       </c>
       <c r="AB639" t="n">
-        <v>7.2</v>
+        <v>53</v>
       </c>
       <c r="AC639" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -85549,7 +85549,7 @@
         </is>
       </c>
       <c r="Y640" s="2" t="n">
-        <v>40072</v>
+        <v>40002</v>
       </c>
       <c r="Z640" t="n">
         <v>0</v>
@@ -85558,11 +85558,11 @@
         <v>0</v>
       </c>
       <c r="AB640" t="n">
-        <v>690</v>
+        <v>6.3</v>
       </c>
       <c r="AC640" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -85682,7 +85682,7 @@
         </is>
       </c>
       <c r="Y641" s="2" t="n">
-        <v>40072</v>
+        <v>40002</v>
       </c>
       <c r="Z641" t="n">
         <v>0</v>
@@ -85691,11 +85691,11 @@
         <v>0</v>
       </c>
       <c r="AB641" t="n">
-        <v>690</v>
+        <v>6.3</v>
       </c>
       <c r="AC641" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -85815,7 +85815,7 @@
         </is>
       </c>
       <c r="Y642" s="2" t="n">
-        <v>40072</v>
+        <v>40009</v>
       </c>
       <c r="Z642" t="n">
         <v>0</v>
@@ -85824,11 +85824,11 @@
         <v>0</v>
       </c>
       <c r="AB642" t="n">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="AC642" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -85948,7 +85948,7 @@
         </is>
       </c>
       <c r="Y643" s="2" t="n">
-        <v>40072</v>
+        <v>40009</v>
       </c>
       <c r="Z643" t="n">
         <v>0</v>
@@ -85957,11 +85957,11 @@
         <v>0</v>
       </c>
       <c r="AB643" t="n">
-        <v>16</v>
+        <v>600</v>
       </c>
       <c r="AC643" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -86081,7 +86081,7 @@
         </is>
       </c>
       <c r="Y644" s="2" t="n">
-        <v>40072</v>
+        <v>40009</v>
       </c>
       <c r="Z644" t="n">
         <v>0</v>
@@ -86090,11 +86090,11 @@
         <v>0</v>
       </c>
       <c r="AB644" t="n">
-        <v>3.2</v>
+        <v>26</v>
       </c>
       <c r="AC644" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -86214,7 +86214,7 @@
         </is>
       </c>
       <c r="Y645" s="2" t="n">
-        <v>40072</v>
+        <v>40009</v>
       </c>
       <c r="Z645" t="n">
         <v>0</v>
@@ -86223,11 +86223,11 @@
         <v>0</v>
       </c>
       <c r="AB645" t="n">
-        <v>3.2</v>
+        <v>26</v>
       </c>
       <c r="AC645" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -86347,7 +86347,7 @@
         </is>
       </c>
       <c r="Y646" s="2" t="n">
-        <v>40079</v>
+        <v>40009</v>
       </c>
       <c r="Z646" t="n">
         <v>0</v>
@@ -86356,11 +86356,11 @@
         <v>0</v>
       </c>
       <c r="AB646" t="n">
-        <v>830</v>
+        <v>7.2</v>
       </c>
       <c r="AC646" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -86480,7 +86480,7 @@
         </is>
       </c>
       <c r="Y647" s="2" t="n">
-        <v>40079</v>
+        <v>40009</v>
       </c>
       <c r="Z647" t="n">
         <v>0</v>
@@ -86489,11 +86489,11 @@
         <v>0</v>
       </c>
       <c r="AB647" t="n">
-        <v>830</v>
+        <v>7.2</v>
       </c>
       <c r="AC647" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -86613,7 +86613,7 @@
         </is>
       </c>
       <c r="Y648" s="2" t="n">
-        <v>40079</v>
+        <v>40072</v>
       </c>
       <c r="Z648" t="n">
         <v>0</v>
@@ -86622,11 +86622,11 @@
         <v>0</v>
       </c>
       <c r="AB648" t="n">
-        <v>23</v>
+        <v>690</v>
       </c>
       <c r="AC648" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -86746,7 +86746,7 @@
         </is>
       </c>
       <c r="Y649" s="2" t="n">
-        <v>40079</v>
+        <v>40072</v>
       </c>
       <c r="Z649" t="n">
         <v>0</v>
@@ -86755,11 +86755,11 @@
         <v>0</v>
       </c>
       <c r="AB649" t="n">
-        <v>23</v>
+        <v>690</v>
       </c>
       <c r="AC649" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -86879,7 +86879,7 @@
         </is>
       </c>
       <c r="Y650" s="2" t="n">
-        <v>40079</v>
+        <v>40072</v>
       </c>
       <c r="Z650" t="n">
         <v>0</v>
@@ -86888,11 +86888,11 @@
         <v>0</v>
       </c>
       <c r="AB650" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="AC650" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -87012,7 +87012,7 @@
         </is>
       </c>
       <c r="Y651" s="2" t="n">
-        <v>40079</v>
+        <v>40072</v>
       </c>
       <c r="Z651" t="n">
         <v>0</v>
@@ -87021,11 +87021,11 @@
         <v>0</v>
       </c>
       <c r="AB651" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="AC651" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -87145,7 +87145,7 @@
         </is>
       </c>
       <c r="Y652" s="2" t="n">
-        <v>40093</v>
+        <v>40072</v>
       </c>
       <c r="Z652" t="n">
         <v>0</v>
@@ -87154,11 +87154,11 @@
         <v>0</v>
       </c>
       <c r="AB652" t="n">
-        <v>4660</v>
+        <v>3.2</v>
       </c>
       <c r="AC652" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -87278,7 +87278,7 @@
         </is>
       </c>
       <c r="Y653" s="2" t="n">
-        <v>40093</v>
+        <v>40072</v>
       </c>
       <c r="Z653" t="n">
         <v>0</v>
@@ -87287,11 +87287,11 @@
         <v>0</v>
       </c>
       <c r="AB653" t="n">
-        <v>4660</v>
+        <v>3.2</v>
       </c>
       <c r="AC653" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -87411,7 +87411,7 @@
         </is>
       </c>
       <c r="Y654" s="2" t="n">
-        <v>40093</v>
+        <v>40079</v>
       </c>
       <c r="Z654" t="n">
         <v>0</v>
@@ -87420,11 +87420,11 @@
         <v>0</v>
       </c>
       <c r="AB654" t="n">
-        <v>218</v>
+        <v>830</v>
       </c>
       <c r="AC654" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -87544,7 +87544,7 @@
         </is>
       </c>
       <c r="Y655" s="2" t="n">
-        <v>40093</v>
+        <v>40079</v>
       </c>
       <c r="Z655" t="n">
         <v>0</v>
@@ -87553,11 +87553,11 @@
         <v>0</v>
       </c>
       <c r="AB655" t="n">
-        <v>218</v>
+        <v>830</v>
       </c>
       <c r="AC655" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -87677,7 +87677,7 @@
         </is>
       </c>
       <c r="Y656" s="2" t="n">
-        <v>40093</v>
+        <v>40079</v>
       </c>
       <c r="Z656" t="n">
         <v>0</v>
@@ -87686,11 +87686,11 @@
         <v>0</v>
       </c>
       <c r="AB656" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="AC656" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -87810,7 +87810,7 @@
         </is>
       </c>
       <c r="Y657" s="2" t="n">
-        <v>40093</v>
+        <v>40079</v>
       </c>
       <c r="Z657" t="n">
         <v>0</v>
@@ -87819,11 +87819,11 @@
         <v>0</v>
       </c>
       <c r="AB657" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="AC657" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -87943,7 +87943,7 @@
         </is>
       </c>
       <c r="Y658" s="2" t="n">
-        <v>40100</v>
+        <v>40079</v>
       </c>
       <c r="Z658" t="n">
         <v>0</v>
@@ -87952,11 +87952,11 @@
         <v>0</v>
       </c>
       <c r="AB658" t="n">
-        <v>1170</v>
+        <v>3.6</v>
       </c>
       <c r="AC658" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -88076,7 +88076,7 @@
         </is>
       </c>
       <c r="Y659" s="2" t="n">
-        <v>40100</v>
+        <v>40079</v>
       </c>
       <c r="Z659" t="n">
         <v>0</v>
@@ -88085,11 +88085,11 @@
         <v>0</v>
       </c>
       <c r="AB659" t="n">
-        <v>1170</v>
+        <v>3.6</v>
       </c>
       <c r="AC659" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -88209,7 +88209,7 @@
         </is>
       </c>
       <c r="Y660" s="2" t="n">
-        <v>40100</v>
+        <v>40093</v>
       </c>
       <c r="Z660" t="n">
         <v>0</v>
@@ -88218,11 +88218,11 @@
         <v>0</v>
       </c>
       <c r="AB660" t="n">
-        <v>34</v>
+        <v>4660</v>
       </c>
       <c r="AC660" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -88342,7 +88342,7 @@
         </is>
       </c>
       <c r="Y661" s="2" t="n">
-        <v>40100</v>
+        <v>40093</v>
       </c>
       <c r="Z661" t="n">
         <v>0</v>
@@ -88351,11 +88351,11 @@
         <v>0</v>
       </c>
       <c r="AB661" t="n">
-        <v>34</v>
+        <v>4660</v>
       </c>
       <c r="AC661" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -88475,7 +88475,7 @@
         </is>
       </c>
       <c r="Y662" s="2" t="n">
-        <v>40100</v>
+        <v>40093</v>
       </c>
       <c r="Z662" t="n">
         <v>0</v>
@@ -88484,11 +88484,11 @@
         <v>0</v>
       </c>
       <c r="AB662" t="n">
-        <v>3.5</v>
+        <v>218</v>
       </c>
       <c r="AC662" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -88608,7 +88608,7 @@
         </is>
       </c>
       <c r="Y663" s="2" t="n">
-        <v>40100</v>
+        <v>40093</v>
       </c>
       <c r="Z663" t="n">
         <v>0</v>
@@ -88617,11 +88617,11 @@
         <v>0</v>
       </c>
       <c r="AB663" t="n">
-        <v>3.5</v>
+        <v>218</v>
       </c>
       <c r="AC663" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -88741,7 +88741,7 @@
         </is>
       </c>
       <c r="Y664" s="2" t="n">
-        <v>40107</v>
+        <v>40093</v>
       </c>
       <c r="Z664" t="n">
         <v>0</v>
@@ -88750,11 +88750,11 @@
         <v>0</v>
       </c>
       <c r="AB664" t="n">
-        <v>1130</v>
+        <v>56</v>
       </c>
       <c r="AC664" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -88874,7 +88874,7 @@
         </is>
       </c>
       <c r="Y665" s="2" t="n">
-        <v>40107</v>
+        <v>40093</v>
       </c>
       <c r="Z665" t="n">
         <v>0</v>
@@ -88883,11 +88883,11 @@
         <v>0</v>
       </c>
       <c r="AB665" t="n">
-        <v>1130</v>
+        <v>56</v>
       </c>
       <c r="AC665" t="inlineStr">
         <is>
-          <t>N-TOT_Ufilt_µg/l N</t>
+          <t>STS_Ufilt_mg/l</t>
         </is>
       </c>
     </row>
@@ -89007,7 +89007,7 @@
         </is>
       </c>
       <c r="Y666" s="2" t="n">
-        <v>40107</v>
+        <v>40100</v>
       </c>
       <c r="Z666" t="n">
         <v>0</v>
@@ -89016,11 +89016,11 @@
         <v>0</v>
       </c>
       <c r="AB666" t="n">
-        <v>17</v>
+        <v>1170</v>
       </c>
       <c r="AC666" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -89140,7 +89140,7 @@
         </is>
       </c>
       <c r="Y667" s="2" t="n">
-        <v>40107</v>
+        <v>40100</v>
       </c>
       <c r="Z667" t="n">
         <v>0</v>
@@ -89149,11 +89149,11 @@
         <v>0</v>
       </c>
       <c r="AB667" t="n">
-        <v>17</v>
+        <v>1170</v>
       </c>
       <c r="AC667" t="inlineStr">
         <is>
-          <t>P-TOT_Ufilt_µg/l P</t>
+          <t>N-TOT_Ufilt_µg/l N</t>
         </is>
       </c>
     </row>
@@ -89273,7 +89273,7 @@
         </is>
       </c>
       <c r="Y668" s="2" t="n">
-        <v>40107</v>
+        <v>40100</v>
       </c>
       <c r="Z668" t="n">
         <v>0</v>
@@ -89282,11 +89282,11 @@
         <v>0</v>
       </c>
       <c r="AB668" t="n">
-        <v>4.6</v>
+        <v>34</v>
       </c>
       <c r="AC668" t="inlineStr">
         <is>
-          <t>STS_Ufilt_mg/l</t>
+          <t>P-TOT_Ufilt_µg/l P</t>
         </is>
       </c>
     </row>
@@ -89406,7 +89406,7 @@
         </is>
       </c>
       <c r="Y669" s="2" t="n">
-        <v>40107</v>
+        <v>40100</v>
       </c>
       <c r="Z669" t="n">
         <v>0</v>
@@ -89415,9 +89415,1073 @@
         <v>0</v>
       </c>
       <c r="AB669" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC669" t="inlineStr">
+        <is>
+          <t>P-TOT_Ufilt_µg/l P</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F670" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W670" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X670" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y670" s="2" t="n">
+        <v>40100</v>
+      </c>
+      <c r="Z670" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA670" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB670" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC670" t="inlineStr">
+        <is>
+          <t>STS_Ufilt_mg/l</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F671" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W671" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X671" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y671" s="2" t="n">
+        <v>40100</v>
+      </c>
+      <c r="Z671" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA671" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB671" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC671" t="inlineStr">
+        <is>
+          <t>STS_Ufilt_mg/l</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F672" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W672" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X672" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y672" s="2" t="n">
+        <v>40107</v>
+      </c>
+      <c r="Z672" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA672" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB672" t="n">
+        <v>1130</v>
+      </c>
+      <c r="AC672" t="inlineStr">
+        <is>
+          <t>N-TOT_Ufilt_µg/l N</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F673" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W673" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X673" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y673" s="2" t="n">
+        <v>40107</v>
+      </c>
+      <c r="Z673" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA673" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB673" t="n">
+        <v>1130</v>
+      </c>
+      <c r="AC673" t="inlineStr">
+        <is>
+          <t>N-TOT_Ufilt_µg/l N</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F674" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W674" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X674" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y674" s="2" t="n">
+        <v>40107</v>
+      </c>
+      <c r="Z674" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA674" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB674" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC674" t="inlineStr">
+        <is>
+          <t>P-TOT_Ufilt_µg/l P</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F675" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W675" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X675" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y675" s="2" t="n">
+        <v>40107</v>
+      </c>
+      <c r="Z675" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA675" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB675" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC675" t="inlineStr">
+        <is>
+          <t>P-TOT_Ufilt_µg/l P</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F676" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W676" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X676" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y676" s="2" t="n">
+        <v>40107</v>
+      </c>
+      <c r="Z676" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA676" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB676" t="n">
         <v>4.6</v>
       </c>
-      <c r="AC669" t="inlineStr">
+      <c r="AC676" t="inlineStr">
+        <is>
+          <t>STS_Ufilt_mg/l</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>63540</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>002-63540</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva (F10)</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>276390.4391999999</v>
+      </c>
+      <c r="F677" t="n">
+        <v>6651962.844799999</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>TILT</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>Tiltaksorientert overvåking</t>
+        </is>
+      </c>
+      <c r="V677" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="W677" t="inlineStr">
+        <is>
+          <t>Lørenskog kommune</t>
+        </is>
+      </c>
+      <c r="X677" t="inlineStr">
+        <is>
+          <t>Ferskvann</t>
+        </is>
+      </c>
+      <c r="Y677" s="2" t="n">
+        <v>40107</v>
+      </c>
+      <c r="Z677" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA677" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB677" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC677" t="inlineStr">
         <is>
           <t>STS_Ufilt_mg/l</t>
         </is>

--- a/data/vannmiljo_duplicates_stations.xlsx
+++ b/data/vannmiljo_duplicates_stations.xlsx
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2070</v>
+        <v>7200</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>7200</v>
+        <v>2070</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.800000000000001</v>
+        <v>410</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>410</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.1</v>
+        <v>84</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>84</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>9.1</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.1</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>22</v>
+        <v>5.7</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>6.1</v>
+        <v>150</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>150</v>
+        <v>6.1</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>16</v>
+        <v>3.3</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>35</v>
+        <v>410</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>410</v>
+        <v>35</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>1</v>
       </c>
       <c r="AB64" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="AB65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>1</v>
       </c>
       <c r="AB68" t="n">
-        <v>42</v>
+        <v>3.9</v>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="AB69" t="n">
-        <v>3.9</v>
+        <v>42</v>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>1</v>
       </c>
       <c r="AB70" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>1</v>
       </c>
       <c r="AB71" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>0</v>
       </c>
       <c r="AB346" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="AC346" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>0</v>
       </c>
       <c r="AB347" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="AC347" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>0</v>
       </c>
       <c r="AB348" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="AC348" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>0</v>
       </c>
       <c r="AB349" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AC349" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>0</v>
       </c>
       <c r="AB350" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="AC350" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>0</v>
       </c>
       <c r="AB351" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="AC351" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>0</v>
       </c>
       <c r="AB352" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AC352" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>0</v>
       </c>
       <c r="AB353" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AC353" t="inlineStr">
         <is>
@@ -47520,7 +47520,7 @@
         <v>0</v>
       </c>
       <c r="AB354" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="AC354" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>0</v>
       </c>
       <c r="AB355" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="AC355" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>0</v>
       </c>
       <c r="AB356" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="AC356" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>0</v>
       </c>
       <c r="AB357" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="AC357" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>0</v>
       </c>
       <c r="AB358" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="AC358" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>0</v>
       </c>
       <c r="AB359" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="AC359" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>0</v>
       </c>
       <c r="AB360" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="AC360" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>0</v>
       </c>
       <c r="AB361" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="AC361" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>0</v>
       </c>
       <c r="AB362" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="AC362" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>0</v>
       </c>
       <c r="AB363" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="AC363" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>0</v>
       </c>
       <c r="AB364" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="AC364" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>0</v>
       </c>
       <c r="AB365" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="AC365" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>0</v>
       </c>
       <c r="AB366" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="AC366" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>0</v>
       </c>
       <c r="AB367" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="AC367" t="inlineStr">
         <is>
@@ -49648,7 +49648,7 @@
         <v>0</v>
       </c>
       <c r="AB370" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AC370" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>0</v>
       </c>
       <c r="AB371" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AC371" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>0</v>
       </c>
       <c r="AB372" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="AC372" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>0</v>
       </c>
       <c r="AB373" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="AC373" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>0</v>
       </c>
       <c r="AB374" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AC374" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>0</v>
       </c>
       <c r="AB375" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AC375" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>1</v>
       </c>
       <c r="AB376" t="n">
-        <v>870</v>
+        <v>970</v>
       </c>
       <c r="AC376" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>1</v>
       </c>
       <c r="AB377" t="n">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="AC377" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>1</v>
       </c>
       <c r="AB380" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AC380" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>1</v>
       </c>
       <c r="AB381" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC381" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>1</v>
       </c>
       <c r="AB386" t="n">
-        <v>1170</v>
+        <v>1090</v>
       </c>
       <c r="AC386" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>1</v>
       </c>
       <c r="AB387" t="n">
-        <v>1090</v>
+        <v>1170</v>
       </c>
       <c r="AC387" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>1</v>
       </c>
       <c r="AB394" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="AC394" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>1</v>
       </c>
       <c r="AB395" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="AC395" t="inlineStr">
         <is>
@@ -53106,7 +53106,7 @@
         <v>1</v>
       </c>
       <c r="AB396" t="n">
-        <v>1280</v>
+        <v>760</v>
       </c>
       <c r="AC396" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>1</v>
       </c>
       <c r="AB397" t="n">
-        <v>760</v>
+        <v>1280</v>
       </c>
       <c r="AC397" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>1</v>
       </c>
       <c r="AB400" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="AC400" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>1</v>
       </c>
       <c r="AB401" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="AC401" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>1</v>
       </c>
       <c r="AB402" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AC402" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>1</v>
       </c>
       <c r="AB403" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AC403" t="inlineStr">
         <is>
@@ -54170,7 +54170,7 @@
         <v>1</v>
       </c>
       <c r="AB404" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AC404" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>1</v>
       </c>
       <c r="AB405" t="n">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="AC405" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>0</v>
       </c>
       <c r="AB408" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AC408" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>0</v>
       </c>
       <c r="AB409" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AC409" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>0</v>
       </c>
       <c r="AB418" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="AC418" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>0</v>
       </c>
       <c r="AB419" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="AC419" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>0</v>
       </c>
       <c r="AB428" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AC428" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>0</v>
       </c>
       <c r="AB429" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AC429" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>0</v>
       </c>
       <c r="AB432" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AC432" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>0</v>
       </c>
       <c r="AB433" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="AC433" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>0</v>
       </c>
       <c r="AB438" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AC438" t="inlineStr">
         <is>
@@ -58825,7 +58825,7 @@
         <v>0</v>
       </c>
       <c r="AB439" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AC439" t="inlineStr">
         <is>
@@ -60022,7 +60022,7 @@
         <v>0</v>
       </c>
       <c r="AB448" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC448" t="inlineStr">
         <is>
@@ -60155,7 +60155,7 @@
         <v>0</v>
       </c>
       <c r="AB449" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC449" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>0</v>
       </c>
       <c r="AB458" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC458" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>0</v>
       </c>
       <c r="AB459" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC459" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>0</v>
       </c>
       <c r="AB468" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AC468" t="inlineStr">
         <is>
@@ -62815,7 +62815,7 @@
         <v>0</v>
       </c>
       <c r="AB469" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AC469" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>0</v>
       </c>
       <c r="AB478" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AC478" t="inlineStr">
         <is>
@@ -64145,7 +64145,7 @@
         <v>0</v>
       </c>
       <c r="AB479" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="AC479" t="inlineStr">
         <is>
@@ -65342,7 +65342,7 @@
         <v>0</v>
       </c>
       <c r="AB488" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AC488" t="inlineStr">
         <is>
@@ -65475,7 +65475,7 @@
         <v>0</v>
       </c>
       <c r="AB489" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AC489" t="inlineStr">
         <is>
@@ -66672,7 +66672,7 @@
         <v>0</v>
       </c>
       <c r="AB498" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC498" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>0</v>
       </c>
       <c r="AB499" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AC499" t="inlineStr">
         <is>
@@ -74120,7 +74120,7 @@
         <v>0</v>
       </c>
       <c r="AB554" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="AC554" t="inlineStr">
         <is>
@@ -74253,7 +74253,7 @@
         <v>0</v>
       </c>
       <c r="AB555" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AC555" t="inlineStr">
         <is>
